--- a/artfynd/A 38667-2026 artfynd.xlsx
+++ b/artfynd/A 38667-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136438472</v>
       </c>
       <c r="B2" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136438476</v>
       </c>
       <c r="B3" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>136438474</v>
       </c>
       <c r="B4" t="n">
-        <v>99370</v>
+        <v>99375</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>136438471</v>
       </c>
       <c r="B5" t="n">
-        <v>102698</v>
+        <v>102703</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>136438475</v>
       </c>
       <c r="B6" t="n">
-        <v>102698</v>
+        <v>102703</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 38667-2026 artfynd.xlsx
+++ b/artfynd/A 38667-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136438472</v>
       </c>
       <c r="B2" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136438476</v>
       </c>
       <c r="B3" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>136438474</v>
       </c>
       <c r="B4" t="n">
-        <v>99375</v>
+        <v>99377</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>136438471</v>
       </c>
       <c r="B5" t="n">
-        <v>102703</v>
+        <v>102705</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>136438475</v>
       </c>
       <c r="B6" t="n">
-        <v>102703</v>
+        <v>102705</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 38667-2026 artfynd.xlsx
+++ b/artfynd/A 38667-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136438472</v>
       </c>
       <c r="B2" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Elvira Ljungberg, Anna Ljunggren, Linus Andersson</t>
+          <t>Linus Andersson, Anna Ljunggren, Elvira Ljungberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -803,7 +803,7 @@
         <v>136438476</v>
       </c>
       <c r="B3" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Elvira Ljungberg, Anna Ljunggren, Linus Andersson</t>
+          <t>Linus Andersson, Anna Ljunggren, Elvira Ljungberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -923,7 +923,7 @@
         <v>136438474</v>
       </c>
       <c r="B4" t="n">
-        <v>99377</v>
+        <v>99383</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elvira Ljungberg, Anna Ljunggren, Linus Andersson</t>
+          <t>Linus Andersson, Anna Ljunggren, Elvira Ljungberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1043,7 +1043,7 @@
         <v>136438471</v>
       </c>
       <c r="B5" t="n">
-        <v>102705</v>
+        <v>102711</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Elvira Ljungberg, Anna Ljunggren, Linus Andersson</t>
+          <t>Linus Andersson, Anna Ljunggren, Elvira Ljungberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1163,7 +1163,7 @@
         <v>136438475</v>
       </c>
       <c r="B6" t="n">
-        <v>102705</v>
+        <v>102711</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Elvira Ljungberg, Anna Ljunggren, Linus Andersson</t>
+          <t>Linus Andersson, Anna Ljunggren, Elvira Ljungberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 38667-2026 artfynd.xlsx
+++ b/artfynd/A 38667-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136438472</v>
       </c>
       <c r="B2" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Linus Andersson, Anna Ljunggren, Elvira Ljungberg</t>
+          <t>Elvira Ljungberg, Anna Ljunggren, Linus Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -803,7 +803,7 @@
         <v>136438476</v>
       </c>
       <c r="B3" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Linus Andersson, Anna Ljunggren, Elvira Ljungberg</t>
+          <t>Elvira Ljungberg, Anna Ljunggren, Linus Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -923,7 +923,7 @@
         <v>136438474</v>
       </c>
       <c r="B4" t="n">
-        <v>99383</v>
+        <v>99385</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Linus Andersson, Anna Ljunggren, Elvira Ljungberg</t>
+          <t>Elvira Ljungberg, Anna Ljunggren, Linus Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1043,7 +1043,7 @@
         <v>136438471</v>
       </c>
       <c r="B5" t="n">
-        <v>102711</v>
+        <v>102713</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linus Andersson, Anna Ljunggren, Elvira Ljungberg</t>
+          <t>Elvira Ljungberg, Anna Ljunggren, Linus Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1163,7 +1163,7 @@
         <v>136438475</v>
       </c>
       <c r="B6" t="n">
-        <v>102711</v>
+        <v>102713</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Linus Andersson, Anna Ljunggren, Elvira Ljungberg</t>
+          <t>Elvira Ljungberg, Anna Ljunggren, Linus Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 38667-2026 artfynd.xlsx
+++ b/artfynd/A 38667-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136438472</v>
       </c>
       <c r="B2" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136438476</v>
       </c>
       <c r="B3" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>136438474</v>
       </c>
       <c r="B4" t="n">
-        <v>99385</v>
+        <v>99386</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>136438471</v>
       </c>
       <c r="B5" t="n">
-        <v>102713</v>
+        <v>102714</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>136438475</v>
       </c>
       <c r="B6" t="n">
-        <v>102713</v>
+        <v>102714</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
